--- a/result/ADAM10_LUSC_Tables.xlsx
+++ b/result/ADAM10_LUSC_Tables.xlsx
@@ -10,8 +10,9 @@
     <sheet name="Table 1 (Chi-square)" sheetId="1" state="visible" r:id="rId1"/>
     <sheet name="Table 2 (Correlation)" sheetId="2" state="visible" r:id="rId2"/>
     <sheet name="Table 3 (Cox)" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="Table 4 (Multivariate OLS)" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="Table 5 (KM Log-rank)" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="Table 3.1 (Cox)_stage_continuous" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Table 4 (Multivariate OLS)" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="Table 5 (KM Log-rank)" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1745,7 +1746,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E6"/>
+  <dimension ref="A1:E8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1778,21 +1779,21 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>ageG</t>
+          <t>age</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1.344</v>
+        <v>1.021</v>
       </c>
       <c r="C2" t="n">
-        <v>0.975</v>
+        <v>1.002</v>
       </c>
       <c r="D2" t="n">
-        <v>1.852</v>
+        <v>1.041</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>0.071</t>
+          <t>0.029</t>
         </is>
       </c>
     </row>
@@ -1806,77 +1807,119 @@
         <v>1</v>
       </c>
       <c r="C3" t="n">
-        <v>0.995</v>
+        <v>0.996</v>
       </c>
       <c r="D3" t="n">
         <v>1.005</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>0.966</t>
+          <t>0.931</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>pathologic_stage</t>
+          <t>ADAM10group_Low</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1.202</v>
+        <v>0.881</v>
       </c>
       <c r="C4" t="n">
-        <v>1.003</v>
+        <v>0.654</v>
       </c>
       <c r="D4" t="n">
-        <v>1.44</v>
+        <v>1.188</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>0.046</t>
+          <t>0.407</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>ADAM10group_Low</t>
+          <t>gender_MALE</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.86</v>
+        <v>1.214</v>
       </c>
       <c r="C5" t="n">
-        <v>0.638</v>
+        <v>0.856</v>
       </c>
       <c r="D5" t="n">
-        <v>1.157</v>
+        <v>1.722</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>0.319</t>
+          <t>0.277</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>gender_MALE</t>
+          <t>pathologic_stage_2.0</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1.212</v>
+        <v>1.027</v>
       </c>
       <c r="C6" t="n">
-        <v>0.857</v>
+        <v>0.725</v>
       </c>
       <c r="D6" t="n">
-        <v>1.715</v>
+        <v>1.455</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>0.276</t>
+          <t>0.880</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>pathologic_stage_3.0</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>1.357</v>
+      </c>
+      <c r="C7" t="n">
+        <v>0.914</v>
+      </c>
+      <c r="D7" t="n">
+        <v>2.015</v>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>0.130</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>pathologic_stage_4.0</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>3.07</v>
+      </c>
+      <c r="C8" t="n">
+        <v>1.224</v>
+      </c>
+      <c r="D8" t="n">
+        <v>7.701</v>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>0.017</t>
         </is>
       </c>
     </row>
@@ -1891,18 +1934,18 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E55"/>
+  <dimension ref="A1:E6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Variable</t>
+          <t>Clinical Variable</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>Coefficient</t>
+          <t>Hazard Ratio (HR)</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
@@ -1922,902 +1965,109 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2">
-        <f>== [ Model: Pathologic Stage ] ===</f>
-        <v/>
-      </c>
-      <c r="B2" t="inlineStr"/>
-      <c r="C2" t="inlineStr"/>
-      <c r="D2" t="inlineStr"/>
-      <c r="E2" t="inlineStr"/>
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>age</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>1.022</v>
+      </c>
+      <c r="C2" t="n">
+        <v>1.003</v>
+      </c>
+      <c r="D2" t="n">
+        <v>1.041</v>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>0.023</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Dependent Variable (Y)</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>ADAM10expression</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr"/>
-      <c r="D3" t="inlineStr"/>
-      <c r="E3" t="inlineStr"/>
+          <t>number_pack_years_smoked</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>1</v>
+      </c>
+      <c r="C3" t="n">
+        <v>0.995</v>
+      </c>
+      <c r="D3" t="n">
+        <v>1.005</v>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>0.992</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Model Formula</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>ADAM10expression ~ age + C(gender) + number_pack_years_smoked + C(pathologic_stage)</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr"/>
-      <c r="D4" t="inlineStr"/>
-      <c r="E4" t="inlineStr"/>
+          <t>pathologic_stage</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>1.202</v>
+      </c>
+      <c r="C4" t="n">
+        <v>1.004</v>
+      </c>
+      <c r="D4" t="n">
+        <v>1.439</v>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>0.046</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>R-squared</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>0.0272</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr"/>
-      <c r="D5" t="inlineStr"/>
-      <c r="E5" t="inlineStr"/>
+          <t>ADAM10group_Low</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>0.874</v>
+      </c>
+      <c r="C5" t="n">
+        <v>0.649</v>
+      </c>
+      <c r="D5" t="n">
+        <v>1.177</v>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>0.375</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Prob (F-statistic)</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>8.2768e-02</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr"/>
-      <c r="D6" t="inlineStr"/>
-      <c r="E6" t="inlineStr"/>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>--- [ Coefficients ] ---</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr"/>
-      <c r="C7" t="inlineStr"/>
-      <c r="D7" t="inlineStr"/>
-      <c r="E7" t="inlineStr"/>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>Intercept</t>
-        </is>
-      </c>
-      <c r="B8" t="n">
-        <v>1153.609</v>
-      </c>
-      <c r="C8" t="n">
-        <v>400.6469</v>
-      </c>
-      <c r="D8" t="n">
-        <v>1906.571</v>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>0.003</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>C(gender)[T.MALE]</t>
-        </is>
-      </c>
-      <c r="B9" t="n">
-        <v>72.8843</v>
-      </c>
-      <c r="C9" t="n">
-        <v>-126.8388</v>
-      </c>
-      <c r="D9" t="n">
-        <v>272.6074</v>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>0.474</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>C(pathologic_stage)[T.2.0]</t>
-        </is>
-      </c>
-      <c r="B10" t="n">
-        <v>-4.8765</v>
-      </c>
-      <c r="C10" t="n">
-        <v>-202.8441</v>
-      </c>
-      <c r="D10" t="n">
-        <v>193.091</v>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>0.961</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>C(pathologic_stage)[T.3.0]</t>
-        </is>
-      </c>
-      <c r="B11" t="n">
-        <v>-102.4179</v>
-      </c>
-      <c r="C11" t="n">
-        <v>-349.6447</v>
-      </c>
-      <c r="D11" t="n">
-        <v>144.8089</v>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>0.416</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>C(pathologic_stage)[T.4.0]</t>
-        </is>
-      </c>
-      <c r="B12" t="n">
-        <v>540.8569</v>
-      </c>
-      <c r="C12" t="n">
-        <v>-191.0502</v>
-      </c>
-      <c r="D12" t="n">
-        <v>1272.7639</v>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>0.147</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>age</t>
-        </is>
-      </c>
-      <c r="B13" t="n">
-        <v>13.9321</v>
-      </c>
-      <c r="C13" t="n">
-        <v>3.3263</v>
-      </c>
-      <c r="D13" t="n">
-        <v>24.5378</v>
-      </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>0.010</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>number_pack_years_smoked</t>
-        </is>
-      </c>
-      <c r="B14" t="n">
-        <v>-0.837</v>
-      </c>
-      <c r="C14" t="n">
-        <v>-3.6433</v>
-      </c>
-      <c r="D14" t="n">
-        <v>1.9694</v>
-      </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>0.558</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr"/>
-      <c r="B15" t="inlineStr"/>
-      <c r="C15" t="inlineStr"/>
-      <c r="D15" t="inlineStr"/>
-      <c r="E15" t="inlineStr"/>
-    </row>
-    <row r="16">
-      <c r="A16">
-        <f>== [ Model: Pathologic T ] ===</f>
-        <v/>
-      </c>
-      <c r="B16" t="inlineStr"/>
-      <c r="C16" t="inlineStr"/>
-      <c r="D16" t="inlineStr"/>
-      <c r="E16" t="inlineStr"/>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>Dependent Variable (Y)</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>ADAM10expression</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr"/>
-      <c r="D17" t="inlineStr"/>
-      <c r="E17" t="inlineStr"/>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>Model Formula</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>ADAM10expression ~ age + C(gender) + number_pack_years_smoked + C(pathologic_T)</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr"/>
-      <c r="D18" t="inlineStr"/>
-      <c r="E18" t="inlineStr"/>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>R-squared</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>0.0212</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr"/>
-      <c r="D19" t="inlineStr"/>
-      <c r="E19" t="inlineStr"/>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>Prob (F-statistic)</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>1.8788e-01</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr"/>
-      <c r="D20" t="inlineStr"/>
-      <c r="E20" t="inlineStr"/>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>--- [ Coefficients ] ---</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr"/>
-      <c r="C21" t="inlineStr"/>
-      <c r="D21" t="inlineStr"/>
-      <c r="E21" t="inlineStr"/>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>Intercept</t>
-        </is>
-      </c>
-      <c r="B22" t="n">
-        <v>1088.7484</v>
-      </c>
-      <c r="C22" t="n">
-        <v>340.9779</v>
-      </c>
-      <c r="D22" t="n">
-        <v>1836.5188</v>
-      </c>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>0.004</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>C(gender)[T.MALE]</t>
-        </is>
-      </c>
-      <c r="B23" t="n">
-        <v>73.50830000000001</v>
-      </c>
-      <c r="C23" t="n">
-        <v>-127.8545</v>
-      </c>
-      <c r="D23" t="n">
-        <v>274.8712</v>
-      </c>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>0.473</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>C(pathologic_T)[T.2.0]</t>
-        </is>
-      </c>
-      <c r="B24" t="n">
-        <v>37.9883</v>
-      </c>
-      <c r="C24" t="n">
-        <v>-177.6533</v>
-      </c>
-      <c r="D24" t="n">
-        <v>253.6299</v>
-      </c>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>0.729</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>C(pathologic_T)[T.3.0]</t>
-        </is>
-      </c>
-      <c r="B25" t="n">
-        <v>-35.3811</v>
-      </c>
-      <c r="C25" t="n">
-        <v>-338.3599</v>
-      </c>
-      <c r="D25" t="n">
-        <v>267.5977</v>
-      </c>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>0.819</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>C(pathologic_T)[T.4.0]</t>
-        </is>
-      </c>
-      <c r="B26" t="n">
-        <v>-119.1889</v>
-      </c>
-      <c r="C26" t="n">
-        <v>-585.625</v>
-      </c>
-      <c r="D26" t="n">
-        <v>347.2473</v>
-      </c>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>0.616</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>age</t>
-        </is>
-      </c>
-      <c r="B27" t="n">
-        <v>14.4734</v>
-      </c>
-      <c r="C27" t="n">
-        <v>3.9399</v>
-      </c>
-      <c r="D27" t="n">
-        <v>25.007</v>
-      </c>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>0.007</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>number_pack_years_smoked</t>
-        </is>
-      </c>
-      <c r="B28" t="n">
-        <v>-0.8356</v>
-      </c>
-      <c r="C28" t="n">
-        <v>-3.6404</v>
-      </c>
-      <c r="D28" t="n">
-        <v>1.9691</v>
-      </c>
-      <c r="E28" t="inlineStr">
-        <is>
-          <t>0.558</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr"/>
-      <c r="B29" t="inlineStr"/>
-      <c r="C29" t="inlineStr"/>
-      <c r="D29" t="inlineStr"/>
-      <c r="E29" t="inlineStr"/>
-    </row>
-    <row r="30">
-      <c r="A30">
-        <f>== [ Model: Pathologic N ] ===</f>
-        <v/>
-      </c>
-      <c r="B30" t="inlineStr"/>
-      <c r="C30" t="inlineStr"/>
-      <c r="D30" t="inlineStr"/>
-      <c r="E30" t="inlineStr"/>
-    </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>Dependent Variable (Y)</t>
-        </is>
-      </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>ADAM10expression</t>
-        </is>
-      </c>
-      <c r="C31" t="inlineStr"/>
-      <c r="D31" t="inlineStr"/>
-      <c r="E31" t="inlineStr"/>
-    </row>
-    <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>Model Formula</t>
-        </is>
-      </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>ADAM10expression ~ age + C(gender) + number_pack_years_smoked + C(pathologic_N)</t>
-        </is>
-      </c>
-      <c r="C32" t="inlineStr"/>
-      <c r="D32" t="inlineStr"/>
-      <c r="E32" t="inlineStr"/>
-    </row>
-    <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>R-squared</t>
-        </is>
-      </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>0.0216</t>
-        </is>
-      </c>
-      <c r="C33" t="inlineStr"/>
-      <c r="D33" t="inlineStr"/>
-      <c r="E33" t="inlineStr"/>
-    </row>
-    <row r="34">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t>Prob (F-statistic)</t>
-        </is>
-      </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>1.8584e-01</t>
-        </is>
-      </c>
-      <c r="C34" t="inlineStr"/>
-      <c r="D34" t="inlineStr"/>
-      <c r="E34" t="inlineStr"/>
-    </row>
-    <row r="35">
-      <c r="A35" t="inlineStr">
-        <is>
-          <t>--- [ Coefficients ] ---</t>
-        </is>
-      </c>
-      <c r="B35" t="inlineStr"/>
-      <c r="C35" t="inlineStr"/>
-      <c r="D35" t="inlineStr"/>
-      <c r="E35" t="inlineStr"/>
-    </row>
-    <row r="36">
-      <c r="A36" t="inlineStr">
-        <is>
-          <t>Intercept</t>
-        </is>
-      </c>
-      <c r="B36" t="n">
-        <v>1128.8198</v>
-      </c>
-      <c r="C36" t="n">
-        <v>365.704</v>
-      </c>
-      <c r="D36" t="n">
-        <v>1891.9356</v>
-      </c>
-      <c r="E36" t="inlineStr">
-        <is>
-          <t>0.004</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" t="inlineStr">
-        <is>
-          <t>C(gender)[T.MALE]</t>
-        </is>
-      </c>
-      <c r="B37" t="n">
-        <v>77.70099999999999</v>
-      </c>
-      <c r="C37" t="n">
-        <v>-122.584</v>
-      </c>
-      <c r="D37" t="n">
-        <v>277.9859</v>
-      </c>
-      <c r="E37" t="inlineStr">
-        <is>
-          <t>0.446</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" t="inlineStr">
-        <is>
-          <t>C(pathologic_N)[T.1.0]</t>
-        </is>
-      </c>
-      <c r="B38" t="n">
-        <v>-51.0047</v>
-      </c>
-      <c r="C38" t="n">
-        <v>-254.5075</v>
-      </c>
-      <c r="D38" t="n">
-        <v>152.4982</v>
-      </c>
-      <c r="E38" t="inlineStr">
-        <is>
-          <t>0.622</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" t="inlineStr">
-        <is>
-          <t>C(pathologic_N)[T.2.0]</t>
-        </is>
-      </c>
-      <c r="B39" t="n">
-        <v>-117.0621</v>
-      </c>
-      <c r="C39" t="n">
-        <v>-446.2089</v>
-      </c>
-      <c r="D39" t="n">
-        <v>212.0848</v>
-      </c>
-      <c r="E39" t="inlineStr">
-        <is>
-          <t>0.485</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" t="inlineStr">
-        <is>
-          <t>C(pathologic_N)[T.3.0]</t>
-        </is>
-      </c>
-      <c r="B40" t="n">
-        <v>126.6878</v>
-      </c>
-      <c r="C40" t="n">
-        <v>-672.6121000000001</v>
-      </c>
-      <c r="D40" t="n">
-        <v>925.9876</v>
-      </c>
-      <c r="E40" t="inlineStr">
-        <is>
-          <t>0.756</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" t="inlineStr">
-        <is>
-          <t>age</t>
-        </is>
-      </c>
-      <c r="B41" t="n">
-        <v>14.306</v>
-      </c>
-      <c r="C41" t="n">
-        <v>3.5073</v>
-      </c>
-      <c r="D41" t="n">
-        <v>25.1046</v>
-      </c>
-      <c r="E41" t="inlineStr">
-        <is>
-          <t>0.010</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" t="inlineStr">
-        <is>
-          <t>number_pack_years_smoked</t>
-        </is>
-      </c>
-      <c r="B42" t="n">
-        <v>-0.7754</v>
-      </c>
-      <c r="C42" t="n">
-        <v>-3.5976</v>
-      </c>
-      <c r="D42" t="n">
-        <v>2.0467</v>
-      </c>
-      <c r="E42" t="inlineStr">
-        <is>
-          <t>0.589</t>
-        </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" t="inlineStr"/>
-      <c r="B43" t="inlineStr"/>
-      <c r="C43" t="inlineStr"/>
-      <c r="D43" t="inlineStr"/>
-      <c r="E43" t="inlineStr"/>
-    </row>
-    <row r="44">
-      <c r="A44">
-        <f>== [ Model: Pathologic M ] ===</f>
-        <v/>
-      </c>
-      <c r="B44" t="inlineStr"/>
-      <c r="C44" t="inlineStr"/>
-      <c r="D44" t="inlineStr"/>
-      <c r="E44" t="inlineStr"/>
-    </row>
-    <row r="45">
-      <c r="A45" t="inlineStr">
-        <is>
-          <t>Dependent Variable (Y)</t>
-        </is>
-      </c>
-      <c r="B45" t="inlineStr">
-        <is>
-          <t>ADAM10expression</t>
-        </is>
-      </c>
-      <c r="C45" t="inlineStr"/>
-      <c r="D45" t="inlineStr"/>
-      <c r="E45" t="inlineStr"/>
-    </row>
-    <row r="46">
-      <c r="A46" t="inlineStr">
-        <is>
-          <t>Model Formula</t>
-        </is>
-      </c>
-      <c r="B46" t="inlineStr">
-        <is>
-          <t>ADAM10expression ~ age + C(gender) + number_pack_years_smoked + C(pathologic_M)</t>
-        </is>
-      </c>
-      <c r="C46" t="inlineStr"/>
-      <c r="D46" t="inlineStr"/>
-      <c r="E46" t="inlineStr"/>
-    </row>
-    <row r="47">
-      <c r="A47" t="inlineStr">
-        <is>
-          <t>R-squared</t>
-        </is>
-      </c>
-      <c r="B47" t="inlineStr">
-        <is>
-          <t>0.0237</t>
-        </is>
-      </c>
-      <c r="C47" t="inlineStr"/>
-      <c r="D47" t="inlineStr"/>
-      <c r="E47" t="inlineStr"/>
-    </row>
-    <row r="48">
-      <c r="A48" t="inlineStr">
-        <is>
-          <t>Prob (F-statistic)</t>
-        </is>
-      </c>
-      <c r="B48" t="inlineStr">
-        <is>
-          <t>8.3717e-02</t>
-        </is>
-      </c>
-      <c r="C48" t="inlineStr"/>
-      <c r="D48" t="inlineStr"/>
-      <c r="E48" t="inlineStr"/>
-    </row>
-    <row r="49">
-      <c r="A49" t="inlineStr">
-        <is>
-          <t>--- [ Coefficients ] ---</t>
-        </is>
-      </c>
-      <c r="B49" t="inlineStr"/>
-      <c r="C49" t="inlineStr"/>
-      <c r="D49" t="inlineStr"/>
-      <c r="E49" t="inlineStr"/>
-    </row>
-    <row r="50">
-      <c r="A50" t="inlineStr">
-        <is>
-          <t>Intercept</t>
-        </is>
-      </c>
-      <c r="B50" t="n">
-        <v>1172.8164</v>
-      </c>
-      <c r="C50" t="n">
-        <v>334.6021</v>
-      </c>
-      <c r="D50" t="n">
-        <v>2011.0308</v>
-      </c>
-      <c r="E50" t="inlineStr">
-        <is>
-          <t>0.006</t>
-        </is>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" t="inlineStr">
-        <is>
-          <t>C(gender)[T.MALE]</t>
-        </is>
-      </c>
-      <c r="B51" t="n">
-        <v>110.4368</v>
-      </c>
-      <c r="C51" t="n">
-        <v>-111.9879</v>
-      </c>
-      <c r="D51" t="n">
-        <v>332.8615</v>
-      </c>
-      <c r="E51" t="inlineStr">
-        <is>
-          <t>0.329</t>
-        </is>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" t="inlineStr">
-        <is>
-          <t>C(pathologic_M)[T.1.0]</t>
-        </is>
-      </c>
-      <c r="B52" t="n">
-        <v>539.2194</v>
-      </c>
-      <c r="C52" t="n">
-        <v>-199.436</v>
-      </c>
-      <c r="D52" t="n">
-        <v>1277.8747</v>
-      </c>
-      <c r="E52" t="inlineStr">
-        <is>
-          <t>0.152</t>
-        </is>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" t="inlineStr">
-        <is>
-          <t>age</t>
-        </is>
-      </c>
-      <c r="B53" t="n">
-        <v>13.203</v>
-      </c>
-      <c r="C53" t="n">
-        <v>1.2918</v>
-      </c>
-      <c r="D53" t="n">
-        <v>25.1142</v>
-      </c>
-      <c r="E53" t="inlineStr">
-        <is>
-          <t>0.030</t>
-        </is>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" t="inlineStr">
-        <is>
-          <t>number_pack_years_smoked</t>
-        </is>
-      </c>
-      <c r="B54" t="n">
-        <v>-0.9345</v>
-      </c>
-      <c r="C54" t="n">
-        <v>-4.0656</v>
-      </c>
-      <c r="D54" t="n">
-        <v>2.1966</v>
-      </c>
-      <c r="E54" t="inlineStr">
-        <is>
-          <t>0.558</t>
-        </is>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" t="inlineStr"/>
-      <c r="B55" t="inlineStr"/>
-      <c r="C55" t="inlineStr"/>
-      <c r="D55" t="inlineStr"/>
-      <c r="E55" t="inlineStr"/>
+          <t>gender_MALE</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>1.227</v>
+      </c>
+      <c r="C6" t="n">
+        <v>0.867</v>
+      </c>
+      <c r="D6" t="n">
+        <v>1.736</v>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>0.248</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -2830,6 +2080,1117 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:E66"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Variable</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Coefficient</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>95% CI Lower</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>95% CI Upper</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>P-value</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2">
+        <f>== [ Model: Base Model (No Stage) ] ===</f>
+        <v/>
+      </c>
+      <c r="B2" t="inlineStr"/>
+      <c r="C2" t="inlineStr"/>
+      <c r="D2" t="inlineStr"/>
+      <c r="E2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Dependent Variable (Y)</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>ADAM10expression</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr"/>
+      <c r="D3" t="inlineStr"/>
+      <c r="E3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Model Formula</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>ADAM10expression ~ age + number_pack_years_smoked + C(gender)</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr"/>
+      <c r="D4" t="inlineStr"/>
+      <c r="E4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>R-squared</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>0.0195</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr"/>
+      <c r="D5" t="inlineStr"/>
+      <c r="E5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Prob (F-statistic)</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>4.5093e-02</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr"/>
+      <c r="D6" t="inlineStr"/>
+      <c r="E6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>--- [ Coefficients ] ---</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr"/>
+      <c r="C7" t="inlineStr"/>
+      <c r="D7" t="inlineStr"/>
+      <c r="E7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Intercept</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>1095.9926</v>
+      </c>
+      <c r="C8" t="n">
+        <v>364.2814</v>
+      </c>
+      <c r="D8" t="n">
+        <v>1827.7038</v>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>0.003</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>C(gender)[T.MALE]</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>78.78579999999999</v>
+      </c>
+      <c r="C9" t="n">
+        <v>-119.4082</v>
+      </c>
+      <c r="D9" t="n">
+        <v>276.9798</v>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>0.435</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>age</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>14.5303</v>
+      </c>
+      <c r="C10" t="n">
+        <v>4.061</v>
+      </c>
+      <c r="D10" t="n">
+        <v>24.9997</v>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>0.007</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>number_pack_years_smoked</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>-0.8641</v>
+      </c>
+      <c r="C11" t="n">
+        <v>-3.6552</v>
+      </c>
+      <c r="D11" t="n">
+        <v>1.927</v>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>0.543</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr"/>
+      <c r="B12" t="inlineStr"/>
+      <c r="C12" t="inlineStr"/>
+      <c r="D12" t="inlineStr"/>
+      <c r="E12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13">
+        <f>== [ Model: Base + Pathologic Stage ] ===</f>
+        <v/>
+      </c>
+      <c r="B13" t="inlineStr"/>
+      <c r="C13" t="inlineStr"/>
+      <c r="D13" t="inlineStr"/>
+      <c r="E13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Dependent Variable (Y)</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>ADAM10expression</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr"/>
+      <c r="D14" t="inlineStr"/>
+      <c r="E14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Model Formula</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>ADAM10expression ~ age + number_pack_years_smoked + C(gender) + C(pathologic_stage)</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr"/>
+      <c r="D15" t="inlineStr"/>
+      <c r="E15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>R-squared</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>0.0272</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr"/>
+      <c r="D16" t="inlineStr"/>
+      <c r="E16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Prob (F-statistic)</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>8.2768e-02</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr"/>
+      <c r="D17" t="inlineStr"/>
+      <c r="E17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>--- [ Coefficients ] ---</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr"/>
+      <c r="C18" t="inlineStr"/>
+      <c r="D18" t="inlineStr"/>
+      <c r="E18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Intercept</t>
+        </is>
+      </c>
+      <c r="B19" t="n">
+        <v>1153.609</v>
+      </c>
+      <c r="C19" t="n">
+        <v>400.6469</v>
+      </c>
+      <c r="D19" t="n">
+        <v>1906.571</v>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>0.003</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>C(gender)[T.MALE]</t>
+        </is>
+      </c>
+      <c r="B20" t="n">
+        <v>72.8843</v>
+      </c>
+      <c r="C20" t="n">
+        <v>-126.8388</v>
+      </c>
+      <c r="D20" t="n">
+        <v>272.6074</v>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>0.474</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>C(pathologic_stage)[T.2.0]</t>
+        </is>
+      </c>
+      <c r="B21" t="n">
+        <v>-4.8765</v>
+      </c>
+      <c r="C21" t="n">
+        <v>-202.8441</v>
+      </c>
+      <c r="D21" t="n">
+        <v>193.091</v>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>0.961</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>C(pathologic_stage)[T.3.0]</t>
+        </is>
+      </c>
+      <c r="B22" t="n">
+        <v>-102.4179</v>
+      </c>
+      <c r="C22" t="n">
+        <v>-349.6447</v>
+      </c>
+      <c r="D22" t="n">
+        <v>144.8089</v>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>0.416</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>C(pathologic_stage)[T.4.0]</t>
+        </is>
+      </c>
+      <c r="B23" t="n">
+        <v>540.8569</v>
+      </c>
+      <c r="C23" t="n">
+        <v>-191.0502</v>
+      </c>
+      <c r="D23" t="n">
+        <v>1272.7639</v>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>0.147</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>age</t>
+        </is>
+      </c>
+      <c r="B24" t="n">
+        <v>13.9321</v>
+      </c>
+      <c r="C24" t="n">
+        <v>3.3263</v>
+      </c>
+      <c r="D24" t="n">
+        <v>24.5378</v>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>0.010</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>number_pack_years_smoked</t>
+        </is>
+      </c>
+      <c r="B25" t="n">
+        <v>-0.837</v>
+      </c>
+      <c r="C25" t="n">
+        <v>-3.6433</v>
+      </c>
+      <c r="D25" t="n">
+        <v>1.9694</v>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>0.558</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr"/>
+      <c r="B26" t="inlineStr"/>
+      <c r="C26" t="inlineStr"/>
+      <c r="D26" t="inlineStr"/>
+      <c r="E26" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27">
+        <f>== [ Model: Base + Pathologic T ] ===</f>
+        <v/>
+      </c>
+      <c r="B27" t="inlineStr"/>
+      <c r="C27" t="inlineStr"/>
+      <c r="D27" t="inlineStr"/>
+      <c r="E27" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>Dependent Variable (Y)</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>ADAM10expression</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr"/>
+      <c r="D28" t="inlineStr"/>
+      <c r="E28" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>Model Formula</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>ADAM10expression ~ age + number_pack_years_smoked + C(gender) + C(pathologic_T)</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr"/>
+      <c r="D29" t="inlineStr"/>
+      <c r="E29" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>R-squared</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>0.0212</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr"/>
+      <c r="D30" t="inlineStr"/>
+      <c r="E30" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Prob (F-statistic)</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>1.8788e-01</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr"/>
+      <c r="D31" t="inlineStr"/>
+      <c r="E31" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>--- [ Coefficients ] ---</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr"/>
+      <c r="C32" t="inlineStr"/>
+      <c r="D32" t="inlineStr"/>
+      <c r="E32" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Intercept</t>
+        </is>
+      </c>
+      <c r="B33" t="n">
+        <v>1088.7484</v>
+      </c>
+      <c r="C33" t="n">
+        <v>340.9779</v>
+      </c>
+      <c r="D33" t="n">
+        <v>1836.5188</v>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>0.004</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>C(gender)[T.MALE]</t>
+        </is>
+      </c>
+      <c r="B34" t="n">
+        <v>73.50830000000001</v>
+      </c>
+      <c r="C34" t="n">
+        <v>-127.8545</v>
+      </c>
+      <c r="D34" t="n">
+        <v>274.8712</v>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>0.473</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>C(pathologic_T)[T.2.0]</t>
+        </is>
+      </c>
+      <c r="B35" t="n">
+        <v>37.9883</v>
+      </c>
+      <c r="C35" t="n">
+        <v>-177.6533</v>
+      </c>
+      <c r="D35" t="n">
+        <v>253.6299</v>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>0.729</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>C(pathologic_T)[T.3.0]</t>
+        </is>
+      </c>
+      <c r="B36" t="n">
+        <v>-35.3811</v>
+      </c>
+      <c r="C36" t="n">
+        <v>-338.3599</v>
+      </c>
+      <c r="D36" t="n">
+        <v>267.5977</v>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>0.819</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>C(pathologic_T)[T.4.0]</t>
+        </is>
+      </c>
+      <c r="B37" t="n">
+        <v>-119.1889</v>
+      </c>
+      <c r="C37" t="n">
+        <v>-585.625</v>
+      </c>
+      <c r="D37" t="n">
+        <v>347.2473</v>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>0.616</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>age</t>
+        </is>
+      </c>
+      <c r="B38" t="n">
+        <v>14.4734</v>
+      </c>
+      <c r="C38" t="n">
+        <v>3.9399</v>
+      </c>
+      <c r="D38" t="n">
+        <v>25.007</v>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>0.007</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>number_pack_years_smoked</t>
+        </is>
+      </c>
+      <c r="B39" t="n">
+        <v>-0.8356</v>
+      </c>
+      <c r="C39" t="n">
+        <v>-3.6404</v>
+      </c>
+      <c r="D39" t="n">
+        <v>1.9691</v>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>0.558</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr"/>
+      <c r="B40" t="inlineStr"/>
+      <c r="C40" t="inlineStr"/>
+      <c r="D40" t="inlineStr"/>
+      <c r="E40" t="inlineStr"/>
+    </row>
+    <row r="41">
+      <c r="A41">
+        <f>== [ Model: Base + Pathologic N ] ===</f>
+        <v/>
+      </c>
+      <c r="B41" t="inlineStr"/>
+      <c r="C41" t="inlineStr"/>
+      <c r="D41" t="inlineStr"/>
+      <c r="E41" t="inlineStr"/>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Dependent Variable (Y)</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>ADAM10expression</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr"/>
+      <c r="D42" t="inlineStr"/>
+      <c r="E42" t="inlineStr"/>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Model Formula</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>ADAM10expression ~ age + number_pack_years_smoked + C(gender) + C(pathologic_N)</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr"/>
+      <c r="D43" t="inlineStr"/>
+      <c r="E43" t="inlineStr"/>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>R-squared</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>0.0216</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr"/>
+      <c r="D44" t="inlineStr"/>
+      <c r="E44" t="inlineStr"/>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Prob (F-statistic)</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>1.8584e-01</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr"/>
+      <c r="D45" t="inlineStr"/>
+      <c r="E45" t="inlineStr"/>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>--- [ Coefficients ] ---</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr"/>
+      <c r="C46" t="inlineStr"/>
+      <c r="D46" t="inlineStr"/>
+      <c r="E46" t="inlineStr"/>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Intercept</t>
+        </is>
+      </c>
+      <c r="B47" t="n">
+        <v>1128.8198</v>
+      </c>
+      <c r="C47" t="n">
+        <v>365.704</v>
+      </c>
+      <c r="D47" t="n">
+        <v>1891.9356</v>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>0.004</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>C(gender)[T.MALE]</t>
+        </is>
+      </c>
+      <c r="B48" t="n">
+        <v>77.70099999999999</v>
+      </c>
+      <c r="C48" t="n">
+        <v>-122.584</v>
+      </c>
+      <c r="D48" t="n">
+        <v>277.9859</v>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>0.446</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>C(pathologic_N)[T.1.0]</t>
+        </is>
+      </c>
+      <c r="B49" t="n">
+        <v>-51.0047</v>
+      </c>
+      <c r="C49" t="n">
+        <v>-254.5075</v>
+      </c>
+      <c r="D49" t="n">
+        <v>152.4982</v>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>0.622</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>C(pathologic_N)[T.2.0]</t>
+        </is>
+      </c>
+      <c r="B50" t="n">
+        <v>-117.0621</v>
+      </c>
+      <c r="C50" t="n">
+        <v>-446.2089</v>
+      </c>
+      <c r="D50" t="n">
+        <v>212.0848</v>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>0.485</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>C(pathologic_N)[T.3.0]</t>
+        </is>
+      </c>
+      <c r="B51" t="n">
+        <v>126.6878</v>
+      </c>
+      <c r="C51" t="n">
+        <v>-672.6121000000001</v>
+      </c>
+      <c r="D51" t="n">
+        <v>925.9876</v>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>0.756</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>age</t>
+        </is>
+      </c>
+      <c r="B52" t="n">
+        <v>14.306</v>
+      </c>
+      <c r="C52" t="n">
+        <v>3.5073</v>
+      </c>
+      <c r="D52" t="n">
+        <v>25.1046</v>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>0.010</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>number_pack_years_smoked</t>
+        </is>
+      </c>
+      <c r="B53" t="n">
+        <v>-0.7754</v>
+      </c>
+      <c r="C53" t="n">
+        <v>-3.5976</v>
+      </c>
+      <c r="D53" t="n">
+        <v>2.0467</v>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>0.589</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr"/>
+      <c r="B54" t="inlineStr"/>
+      <c r="C54" t="inlineStr"/>
+      <c r="D54" t="inlineStr"/>
+      <c r="E54" t="inlineStr"/>
+    </row>
+    <row r="55">
+      <c r="A55">
+        <f>== [ Model: Base + Pathologic M ] ===</f>
+        <v/>
+      </c>
+      <c r="B55" t="inlineStr"/>
+      <c r="C55" t="inlineStr"/>
+      <c r="D55" t="inlineStr"/>
+      <c r="E55" t="inlineStr"/>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>Dependent Variable (Y)</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>ADAM10expression</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr"/>
+      <c r="D56" t="inlineStr"/>
+      <c r="E56" t="inlineStr"/>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>Model Formula</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>ADAM10expression ~ age + number_pack_years_smoked + C(gender) + C(pathologic_M)</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr"/>
+      <c r="D57" t="inlineStr"/>
+      <c r="E57" t="inlineStr"/>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>R-squared</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>0.0237</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr"/>
+      <c r="D58" t="inlineStr"/>
+      <c r="E58" t="inlineStr"/>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>Prob (F-statistic)</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>8.3717e-02</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr"/>
+      <c r="D59" t="inlineStr"/>
+      <c r="E59" t="inlineStr"/>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>--- [ Coefficients ] ---</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr"/>
+      <c r="C60" t="inlineStr"/>
+      <c r="D60" t="inlineStr"/>
+      <c r="E60" t="inlineStr"/>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>Intercept</t>
+        </is>
+      </c>
+      <c r="B61" t="n">
+        <v>1172.8164</v>
+      </c>
+      <c r="C61" t="n">
+        <v>334.6021</v>
+      </c>
+      <c r="D61" t="n">
+        <v>2011.0308</v>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>0.006</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>C(gender)[T.MALE]</t>
+        </is>
+      </c>
+      <c r="B62" t="n">
+        <v>110.4368</v>
+      </c>
+      <c r="C62" t="n">
+        <v>-111.9879</v>
+      </c>
+      <c r="D62" t="n">
+        <v>332.8615</v>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>0.329</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>C(pathologic_M)[T.1.0]</t>
+        </is>
+      </c>
+      <c r="B63" t="n">
+        <v>539.2194</v>
+      </c>
+      <c r="C63" t="n">
+        <v>-199.436</v>
+      </c>
+      <c r="D63" t="n">
+        <v>1277.8747</v>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>0.152</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>age</t>
+        </is>
+      </c>
+      <c r="B64" t="n">
+        <v>13.203</v>
+      </c>
+      <c r="C64" t="n">
+        <v>1.2918</v>
+      </c>
+      <c r="D64" t="n">
+        <v>25.1142</v>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>0.030</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>number_pack_years_smoked</t>
+        </is>
+      </c>
+      <c r="B65" t="n">
+        <v>-0.9345</v>
+      </c>
+      <c r="C65" t="n">
+        <v>-4.0656</v>
+      </c>
+      <c r="D65" t="n">
+        <v>2.1966</v>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>0.558</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr"/>
+      <c r="B66" t="inlineStr"/>
+      <c r="C66" t="inlineStr"/>
+      <c r="D66" t="inlineStr"/>
+      <c r="E66" t="inlineStr"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:E3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>

--- a/result/ADAM10_LUSC_Tables.xlsx
+++ b/result/ADAM10_LUSC_Tables.xlsx
@@ -430,7 +430,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E28"/>
+  <dimension ref="A1:D28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -439,18 +439,17 @@
           <t>Clinical Characteristics</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr"/>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>P-value</t>
         </is>
@@ -465,7 +464,6 @@
       <c r="B2" t="inlineStr"/>
       <c r="C2" t="inlineStr"/>
       <c r="D2" t="inlineStr"/>
-      <c r="E2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -474,17 +472,14 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0</v>
+        <v>86</v>
       </c>
       <c r="C3" t="n">
-        <v>86</v>
-      </c>
-      <c r="D3" t="n">
         <v>103</v>
       </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>0.197</t>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>0.106</t>
         </is>
       </c>
     </row>
@@ -495,15 +490,12 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1</v>
+        <v>158</v>
       </c>
       <c r="C4" t="n">
-        <v>158</v>
-      </c>
-      <c r="D4" t="n">
         <v>140</v>
       </c>
-      <c r="E4" t="inlineStr"/>
+      <c r="D4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -514,7 +506,6 @@
       <c r="B5" t="inlineStr"/>
       <c r="C5" t="inlineStr"/>
       <c r="D5" t="inlineStr"/>
-      <c r="E5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -523,17 +514,14 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1</v>
+        <v>61</v>
       </c>
       <c r="C6" t="n">
-        <v>61</v>
-      </c>
-      <c r="D6" t="n">
         <v>64</v>
       </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>0.224</t>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>0.735</t>
         </is>
       </c>
     </row>
@@ -544,15 +532,12 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0</v>
+        <v>183</v>
       </c>
       <c r="C7" t="n">
-        <v>183</v>
-      </c>
-      <c r="D7" t="n">
         <v>179</v>
       </c>
-      <c r="E7" t="inlineStr"/>
+      <c r="D7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -563,7 +548,6 @@
       <c r="B8" t="inlineStr"/>
       <c r="C8" t="inlineStr"/>
       <c r="D8" t="inlineStr"/>
-      <c r="E8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -572,17 +556,14 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0</v>
+        <v>121</v>
       </c>
       <c r="C9" t="n">
-        <v>121</v>
-      </c>
-      <c r="D9" t="n">
         <v>117</v>
       </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>0.876</t>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>0.955</t>
         </is>
       </c>
     </row>
@@ -593,15 +574,12 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>1</v>
+        <v>79</v>
       </c>
       <c r="C10" t="n">
-        <v>79</v>
-      </c>
-      <c r="D10" t="n">
         <v>76</v>
       </c>
-      <c r="E10" t="inlineStr"/>
+      <c r="D10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -610,15 +588,12 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="C11" t="n">
-        <v>40</v>
-      </c>
-      <c r="D11" t="n">
         <v>43</v>
       </c>
-      <c r="E11" t="inlineStr"/>
+      <c r="D11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -627,15 +602,12 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="C12" t="n">
-        <v>4</v>
-      </c>
-      <c r="D12" t="n">
         <v>3</v>
       </c>
-      <c r="E12" t="inlineStr"/>
+      <c r="D12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -646,7 +618,6 @@
       <c r="B13" t="inlineStr"/>
       <c r="C13" t="inlineStr"/>
       <c r="D13" t="inlineStr"/>
-      <c r="E13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -655,17 +626,14 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>1</v>
+        <v>195</v>
       </c>
       <c r="C14" t="n">
-        <v>195</v>
-      </c>
-      <c r="D14" t="n">
         <v>205</v>
       </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>0.899</t>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>0.660</t>
         </is>
       </c>
     </row>
@@ -676,15 +644,12 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="C15" t="n">
-        <v>4</v>
-      </c>
-      <c r="D15" t="n">
         <v>3</v>
       </c>
-      <c r="E15" t="inlineStr"/>
+      <c r="D15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -695,7 +660,6 @@
       <c r="B16" t="inlineStr"/>
       <c r="C16" t="inlineStr"/>
       <c r="D16" t="inlineStr"/>
-      <c r="E16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -704,17 +668,14 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>0</v>
+        <v>159</v>
       </c>
       <c r="C17" t="n">
-        <v>159</v>
-      </c>
-      <c r="D17" t="n">
         <v>152</v>
       </c>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>0.731</t>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>0.858</t>
         </is>
       </c>
     </row>
@@ -725,15 +686,12 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>1</v>
+        <v>62</v>
       </c>
       <c r="C18" t="n">
-        <v>62</v>
-      </c>
-      <c r="D18" t="n">
         <v>63</v>
       </c>
-      <c r="E18" t="inlineStr"/>
+      <c r="D18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -742,15 +700,12 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="C19" t="n">
-        <v>18</v>
-      </c>
-      <c r="D19" t="n">
         <v>22</v>
       </c>
-      <c r="E19" t="inlineStr"/>
+      <c r="D19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -759,15 +714,12 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="C20" t="n">
-        <v>2</v>
-      </c>
-      <c r="D20" t="n">
         <v>3</v>
       </c>
-      <c r="E20" t="inlineStr"/>
+      <c r="D20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -778,7 +730,6 @@
       <c r="B21" t="inlineStr"/>
       <c r="C21" t="inlineStr"/>
       <c r="D21" t="inlineStr"/>
-      <c r="E21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -787,17 +738,14 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>1</v>
+        <v>56</v>
       </c>
       <c r="C22" t="n">
-        <v>56</v>
-      </c>
-      <c r="D22" t="n">
         <v>52</v>
       </c>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>0.635</t>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>0.844</t>
         </is>
       </c>
     </row>
@@ -808,15 +756,12 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>0</v>
+        <v>141</v>
       </c>
       <c r="C23" t="n">
-        <v>141</v>
-      </c>
-      <c r="D23" t="n">
         <v>145</v>
       </c>
-      <c r="E23" t="inlineStr"/>
+      <c r="D23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -825,15 +770,12 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>0</v>
+        <v>37</v>
       </c>
       <c r="C24" t="n">
-        <v>37</v>
-      </c>
-      <c r="D24" t="n">
         <v>33</v>
       </c>
-      <c r="E24" t="inlineStr"/>
+      <c r="D24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -842,15 +784,12 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="C25" t="n">
-        <v>10</v>
-      </c>
-      <c r="D25" t="n">
         <v>13</v>
       </c>
-      <c r="E25" t="inlineStr"/>
+      <c r="D25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -861,7 +800,6 @@
       <c r="B26" t="inlineStr"/>
       <c r="C26" t="inlineStr"/>
       <c r="D26" t="inlineStr"/>
-      <c r="E26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -870,17 +808,14 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>1</v>
+        <v>40</v>
       </c>
       <c r="C27" t="n">
-        <v>40</v>
-      </c>
-      <c r="D27" t="n">
         <v>35</v>
       </c>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>0.054</t>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>0.530</t>
         </is>
       </c>
     </row>
@@ -891,15 +826,12 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>0</v>
+        <v>204</v>
       </c>
       <c r="C28" t="n">
-        <v>204</v>
-      </c>
-      <c r="D28" t="n">
         <v>209</v>
       </c>
-      <c r="E28" t="inlineStr"/>
+      <c r="D28" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/result/ADAM10_LUSC_Tables.xlsx
+++ b/result/ADAM10_LUSC_Tables.xlsx
@@ -1678,7 +1678,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E8"/>
+  <dimension ref="A1:D8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1694,15 +1694,10 @@
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>95% CI Lower</t>
+          <t>95% CI</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>95% CI Upper</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>P-value</t>
         </is>
@@ -1717,13 +1712,12 @@
       <c r="B2" t="n">
         <v>1.021</v>
       </c>
-      <c r="C2" t="n">
-        <v>1.002</v>
-      </c>
-      <c r="D2" t="n">
-        <v>1.041</v>
-      </c>
-      <c r="E2" t="inlineStr">
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>1.002-1.041</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
         <is>
           <t>0.029</t>
         </is>
@@ -1738,13 +1732,12 @@
       <c r="B3" t="n">
         <v>1</v>
       </c>
-      <c r="C3" t="n">
-        <v>0.996</v>
-      </c>
-      <c r="D3" t="n">
-        <v>1.005</v>
-      </c>
-      <c r="E3" t="inlineStr">
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>0.996-1.005</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
         <is>
           <t>0.931</t>
         </is>
@@ -1759,13 +1752,12 @@
       <c r="B4" t="n">
         <v>0.881</v>
       </c>
-      <c r="C4" t="n">
-        <v>0.654</v>
-      </c>
-      <c r="D4" t="n">
-        <v>1.188</v>
-      </c>
-      <c r="E4" t="inlineStr">
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>0.654-1.188</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
         <is>
           <t>0.407</t>
         </is>
@@ -1780,13 +1772,12 @@
       <c r="B5" t="n">
         <v>1.214</v>
       </c>
-      <c r="C5" t="n">
-        <v>0.856</v>
-      </c>
-      <c r="D5" t="n">
-        <v>1.722</v>
-      </c>
-      <c r="E5" t="inlineStr">
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>0.856-1.722</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
         <is>
           <t>0.277</t>
         </is>
@@ -1801,13 +1792,12 @@
       <c r="B6" t="n">
         <v>1.027</v>
       </c>
-      <c r="C6" t="n">
-        <v>0.725</v>
-      </c>
-      <c r="D6" t="n">
-        <v>1.455</v>
-      </c>
-      <c r="E6" t="inlineStr">
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>0.725-1.455</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
         <is>
           <t>0.880</t>
         </is>
@@ -1822,13 +1812,12 @@
       <c r="B7" t="n">
         <v>1.357</v>
       </c>
-      <c r="C7" t="n">
-        <v>0.914</v>
-      </c>
-      <c r="D7" t="n">
-        <v>2.015</v>
-      </c>
-      <c r="E7" t="inlineStr">
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>0.914-2.015</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
         <is>
           <t>0.130</t>
         </is>
@@ -1843,13 +1832,12 @@
       <c r="B8" t="n">
         <v>3.07</v>
       </c>
-      <c r="C8" t="n">
-        <v>1.224</v>
-      </c>
-      <c r="D8" t="n">
-        <v>7.701</v>
-      </c>
-      <c r="E8" t="inlineStr">
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>1.224-7.701</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
         <is>
           <t>0.017</t>
         </is>
@@ -1866,7 +1854,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E6"/>
+  <dimension ref="A1:D6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1882,15 +1870,10 @@
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>95% CI Lower</t>
+          <t>95% CI</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>95% CI Upper</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>P-value</t>
         </is>
@@ -1905,13 +1888,12 @@
       <c r="B2" t="n">
         <v>1.022</v>
       </c>
-      <c r="C2" t="n">
-        <v>1.003</v>
-      </c>
-      <c r="D2" t="n">
-        <v>1.041</v>
-      </c>
-      <c r="E2" t="inlineStr">
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>1.003-1.041</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
         <is>
           <t>0.023</t>
         </is>
@@ -1926,13 +1908,12 @@
       <c r="B3" t="n">
         <v>1</v>
       </c>
-      <c r="C3" t="n">
-        <v>0.995</v>
-      </c>
-      <c r="D3" t="n">
-        <v>1.005</v>
-      </c>
-      <c r="E3" t="inlineStr">
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>0.995-1.005</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
         <is>
           <t>0.992</t>
         </is>
@@ -1947,13 +1928,12 @@
       <c r="B4" t="n">
         <v>1.202</v>
       </c>
-      <c r="C4" t="n">
-        <v>1.004</v>
-      </c>
-      <c r="D4" t="n">
-        <v>1.439</v>
-      </c>
-      <c r="E4" t="inlineStr">
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>1.004-1.439</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
         <is>
           <t>0.046</t>
         </is>
@@ -1968,13 +1948,12 @@
       <c r="B5" t="n">
         <v>0.874</v>
       </c>
-      <c r="C5" t="n">
-        <v>0.649</v>
-      </c>
-      <c r="D5" t="n">
-        <v>1.177</v>
-      </c>
-      <c r="E5" t="inlineStr">
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>0.649-1.177</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
         <is>
           <t>0.375</t>
         </is>
@@ -1989,13 +1968,12 @@
       <c r="B6" t="n">
         <v>1.227</v>
       </c>
-      <c r="C6" t="n">
-        <v>0.867</v>
-      </c>
-      <c r="D6" t="n">
-        <v>1.736</v>
-      </c>
-      <c r="E6" t="inlineStr">
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>0.867-1.736</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
         <is>
           <t>0.248</t>
         </is>
@@ -2012,7 +1990,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E66"/>
+  <dimension ref="A1:D66"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2028,15 +2006,10 @@
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>95% CI Lower</t>
+          <t>95% CI</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>95% CI Upper</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>P-value</t>
         </is>
@@ -2050,7 +2023,6 @@
       <c r="B2" t="inlineStr"/>
       <c r="C2" t="inlineStr"/>
       <c r="D2" t="inlineStr"/>
-      <c r="E2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -2065,7 +2037,6 @@
       </c>
       <c r="C3" t="inlineStr"/>
       <c r="D3" t="inlineStr"/>
-      <c r="E3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -2080,7 +2051,6 @@
       </c>
       <c r="C4" t="inlineStr"/>
       <c r="D4" t="inlineStr"/>
-      <c r="E4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -2095,7 +2065,6 @@
       </c>
       <c r="C5" t="inlineStr"/>
       <c r="D5" t="inlineStr"/>
-      <c r="E5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -2110,7 +2079,6 @@
       </c>
       <c r="C6" t="inlineStr"/>
       <c r="D6" t="inlineStr"/>
-      <c r="E6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -2121,7 +2089,6 @@
       <c r="B7" t="inlineStr"/>
       <c r="C7" t="inlineStr"/>
       <c r="D7" t="inlineStr"/>
-      <c r="E7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -2130,15 +2097,14 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>1095.9926</v>
-      </c>
-      <c r="C8" t="n">
-        <v>364.2814</v>
-      </c>
-      <c r="D8" t="n">
-        <v>1827.7038</v>
-      </c>
-      <c r="E8" t="inlineStr">
+        <v>1095.993</v>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>364.281-1827.704</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
         <is>
           <t>0.003</t>
         </is>
@@ -2151,15 +2117,14 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>78.78579999999999</v>
-      </c>
-      <c r="C9" t="n">
-        <v>-119.4082</v>
-      </c>
-      <c r="D9" t="n">
-        <v>276.9798</v>
-      </c>
-      <c r="E9" t="inlineStr">
+        <v>78.786</v>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>-119.408-276.98</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
         <is>
           <t>0.435</t>
         </is>
@@ -2172,15 +2137,14 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>14.5303</v>
-      </c>
-      <c r="C10" t="n">
-        <v>4.061</v>
-      </c>
-      <c r="D10" t="n">
-        <v>24.9997</v>
-      </c>
-      <c r="E10" t="inlineStr">
+        <v>14.53</v>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>4.061-25.0</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
         <is>
           <t>0.007</t>
         </is>
@@ -2193,15 +2157,14 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>-0.8641</v>
-      </c>
-      <c r="C11" t="n">
-        <v>-3.6552</v>
-      </c>
-      <c r="D11" t="n">
-        <v>1.927</v>
-      </c>
-      <c r="E11" t="inlineStr">
+        <v>-0.864</v>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>-3.655-1.927</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
         <is>
           <t>0.543</t>
         </is>
@@ -2212,7 +2175,6 @@
       <c r="B12" t="inlineStr"/>
       <c r="C12" t="inlineStr"/>
       <c r="D12" t="inlineStr"/>
-      <c r="E12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13">
@@ -2222,7 +2184,6 @@
       <c r="B13" t="inlineStr"/>
       <c r="C13" t="inlineStr"/>
       <c r="D13" t="inlineStr"/>
-      <c r="E13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -2237,7 +2198,6 @@
       </c>
       <c r="C14" t="inlineStr"/>
       <c r="D14" t="inlineStr"/>
-      <c r="E14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -2252,7 +2212,6 @@
       </c>
       <c r="C15" t="inlineStr"/>
       <c r="D15" t="inlineStr"/>
-      <c r="E15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -2267,7 +2226,6 @@
       </c>
       <c r="C16" t="inlineStr"/>
       <c r="D16" t="inlineStr"/>
-      <c r="E16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -2282,7 +2240,6 @@
       </c>
       <c r="C17" t="inlineStr"/>
       <c r="D17" t="inlineStr"/>
-      <c r="E17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -2293,7 +2250,6 @@
       <c r="B18" t="inlineStr"/>
       <c r="C18" t="inlineStr"/>
       <c r="D18" t="inlineStr"/>
-      <c r="E18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -2304,13 +2260,12 @@
       <c r="B19" t="n">
         <v>1153.609</v>
       </c>
-      <c r="C19" t="n">
-        <v>400.6469</v>
-      </c>
-      <c r="D19" t="n">
-        <v>1906.571</v>
-      </c>
-      <c r="E19" t="inlineStr">
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>400.647-1906.571</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
         <is>
           <t>0.003</t>
         </is>
@@ -2323,15 +2278,14 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>72.8843</v>
-      </c>
-      <c r="C20" t="n">
-        <v>-126.8388</v>
-      </c>
-      <c r="D20" t="n">
-        <v>272.6074</v>
-      </c>
-      <c r="E20" t="inlineStr">
+        <v>72.884</v>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>-126.839-272.607</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
         <is>
           <t>0.474</t>
         </is>
@@ -2344,15 +2298,14 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>-4.8765</v>
-      </c>
-      <c r="C21" t="n">
-        <v>-202.8441</v>
-      </c>
-      <c r="D21" t="n">
-        <v>193.091</v>
-      </c>
-      <c r="E21" t="inlineStr">
+        <v>-4.877</v>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>-202.844-193.091</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
         <is>
           <t>0.961</t>
         </is>
@@ -2365,15 +2318,14 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>-102.4179</v>
-      </c>
-      <c r="C22" t="n">
-        <v>-349.6447</v>
-      </c>
-      <c r="D22" t="n">
-        <v>144.8089</v>
-      </c>
-      <c r="E22" t="inlineStr">
+        <v>-102.418</v>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>-349.645-144.809</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
         <is>
           <t>0.416</t>
         </is>
@@ -2386,15 +2338,14 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>540.8569</v>
-      </c>
-      <c r="C23" t="n">
-        <v>-191.0502</v>
-      </c>
-      <c r="D23" t="n">
-        <v>1272.7639</v>
-      </c>
-      <c r="E23" t="inlineStr">
+        <v>540.857</v>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>-191.05-1272.764</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
         <is>
           <t>0.147</t>
         </is>
@@ -2407,15 +2358,14 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>13.9321</v>
-      </c>
-      <c r="C24" t="n">
-        <v>3.3263</v>
-      </c>
-      <c r="D24" t="n">
-        <v>24.5378</v>
-      </c>
-      <c r="E24" t="inlineStr">
+        <v>13.932</v>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>3.326-24.538</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
         <is>
           <t>0.010</t>
         </is>
@@ -2430,13 +2380,12 @@
       <c r="B25" t="n">
         <v>-0.837</v>
       </c>
-      <c r="C25" t="n">
-        <v>-3.6433</v>
-      </c>
-      <c r="D25" t="n">
-        <v>1.9694</v>
-      </c>
-      <c r="E25" t="inlineStr">
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>-3.643-1.969</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
         <is>
           <t>0.558</t>
         </is>
@@ -2447,7 +2396,6 @@
       <c r="B26" t="inlineStr"/>
       <c r="C26" t="inlineStr"/>
       <c r="D26" t="inlineStr"/>
-      <c r="E26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27">
@@ -2457,7 +2405,6 @@
       <c r="B27" t="inlineStr"/>
       <c r="C27" t="inlineStr"/>
       <c r="D27" t="inlineStr"/>
-      <c r="E27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -2472,7 +2419,6 @@
       </c>
       <c r="C28" t="inlineStr"/>
       <c r="D28" t="inlineStr"/>
-      <c r="E28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -2487,7 +2433,6 @@
       </c>
       <c r="C29" t="inlineStr"/>
       <c r="D29" t="inlineStr"/>
-      <c r="E29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -2502,7 +2447,6 @@
       </c>
       <c r="C30" t="inlineStr"/>
       <c r="D30" t="inlineStr"/>
-      <c r="E30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -2517,7 +2461,6 @@
       </c>
       <c r="C31" t="inlineStr"/>
       <c r="D31" t="inlineStr"/>
-      <c r="E31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -2528,7 +2471,6 @@
       <c r="B32" t="inlineStr"/>
       <c r="C32" t="inlineStr"/>
       <c r="D32" t="inlineStr"/>
-      <c r="E32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -2537,15 +2479,14 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>1088.7484</v>
-      </c>
-      <c r="C33" t="n">
-        <v>340.9779</v>
-      </c>
-      <c r="D33" t="n">
-        <v>1836.5188</v>
-      </c>
-      <c r="E33" t="inlineStr">
+        <v>1088.748</v>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>340.978-1836.519</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
         <is>
           <t>0.004</t>
         </is>
@@ -2558,15 +2499,14 @@
         </is>
       </c>
       <c r="B34" t="n">
-        <v>73.50830000000001</v>
-      </c>
-      <c r="C34" t="n">
-        <v>-127.8545</v>
-      </c>
-      <c r="D34" t="n">
-        <v>274.8712</v>
-      </c>
-      <c r="E34" t="inlineStr">
+        <v>73.508</v>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>-127.855-274.871</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
         <is>
           <t>0.473</t>
         </is>
@@ -2579,15 +2519,14 @@
         </is>
       </c>
       <c r="B35" t="n">
-        <v>37.9883</v>
-      </c>
-      <c r="C35" t="n">
-        <v>-177.6533</v>
-      </c>
-      <c r="D35" t="n">
-        <v>253.6299</v>
-      </c>
-      <c r="E35" t="inlineStr">
+        <v>37.988</v>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>-177.653-253.63</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
         <is>
           <t>0.729</t>
         </is>
@@ -2600,15 +2539,14 @@
         </is>
       </c>
       <c r="B36" t="n">
-        <v>-35.3811</v>
-      </c>
-      <c r="C36" t="n">
-        <v>-338.3599</v>
-      </c>
-      <c r="D36" t="n">
-        <v>267.5977</v>
-      </c>
-      <c r="E36" t="inlineStr">
+        <v>-35.381</v>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>-338.36-267.598</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
         <is>
           <t>0.819</t>
         </is>
@@ -2621,15 +2559,14 @@
         </is>
       </c>
       <c r="B37" t="n">
-        <v>-119.1889</v>
-      </c>
-      <c r="C37" t="n">
-        <v>-585.625</v>
-      </c>
-      <c r="D37" t="n">
-        <v>347.2473</v>
-      </c>
-      <c r="E37" t="inlineStr">
+        <v>-119.189</v>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>-585.625-347.247</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
         <is>
           <t>0.616</t>
         </is>
@@ -2642,15 +2579,14 @@
         </is>
       </c>
       <c r="B38" t="n">
-        <v>14.4734</v>
-      </c>
-      <c r="C38" t="n">
-        <v>3.9399</v>
-      </c>
-      <c r="D38" t="n">
-        <v>25.007</v>
-      </c>
-      <c r="E38" t="inlineStr">
+        <v>14.473</v>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>3.94-25.007</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
         <is>
           <t>0.007</t>
         </is>
@@ -2663,15 +2599,14 @@
         </is>
       </c>
       <c r="B39" t="n">
-        <v>-0.8356</v>
-      </c>
-      <c r="C39" t="n">
-        <v>-3.6404</v>
-      </c>
-      <c r="D39" t="n">
-        <v>1.9691</v>
-      </c>
-      <c r="E39" t="inlineStr">
+        <v>-0.836</v>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>-3.64-1.969</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
         <is>
           <t>0.558</t>
         </is>
@@ -2682,7 +2617,6 @@
       <c r="B40" t="inlineStr"/>
       <c r="C40" t="inlineStr"/>
       <c r="D40" t="inlineStr"/>
-      <c r="E40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41">
@@ -2692,7 +2626,6 @@
       <c r="B41" t="inlineStr"/>
       <c r="C41" t="inlineStr"/>
       <c r="D41" t="inlineStr"/>
-      <c r="E41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -2707,7 +2640,6 @@
       </c>
       <c r="C42" t="inlineStr"/>
       <c r="D42" t="inlineStr"/>
-      <c r="E42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -2722,7 +2654,6 @@
       </c>
       <c r="C43" t="inlineStr"/>
       <c r="D43" t="inlineStr"/>
-      <c r="E43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -2737,7 +2668,6 @@
       </c>
       <c r="C44" t="inlineStr"/>
       <c r="D44" t="inlineStr"/>
-      <c r="E44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -2752,7 +2682,6 @@
       </c>
       <c r="C45" t="inlineStr"/>
       <c r="D45" t="inlineStr"/>
-      <c r="E45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -2763,7 +2692,6 @@
       <c r="B46" t="inlineStr"/>
       <c r="C46" t="inlineStr"/>
       <c r="D46" t="inlineStr"/>
-      <c r="E46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -2772,15 +2700,14 @@
         </is>
       </c>
       <c r="B47" t="n">
-        <v>1128.8198</v>
-      </c>
-      <c r="C47" t="n">
-        <v>365.704</v>
-      </c>
-      <c r="D47" t="n">
-        <v>1891.9356</v>
-      </c>
-      <c r="E47" t="inlineStr">
+        <v>1128.82</v>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>365.704-1891.936</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
         <is>
           <t>0.004</t>
         </is>
@@ -2795,13 +2722,12 @@
       <c r="B48" t="n">
         <v>77.70099999999999</v>
       </c>
-      <c r="C48" t="n">
-        <v>-122.584</v>
-      </c>
-      <c r="D48" t="n">
-        <v>277.9859</v>
-      </c>
-      <c r="E48" t="inlineStr">
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>-122.584-277.986</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
         <is>
           <t>0.446</t>
         </is>
@@ -2814,15 +2740,14 @@
         </is>
       </c>
       <c r="B49" t="n">
-        <v>-51.0047</v>
-      </c>
-      <c r="C49" t="n">
-        <v>-254.5075</v>
-      </c>
-      <c r="D49" t="n">
-        <v>152.4982</v>
-      </c>
-      <c r="E49" t="inlineStr">
+        <v>-51.005</v>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>-254.508-152.498</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
         <is>
           <t>0.622</t>
         </is>
@@ -2835,15 +2760,14 @@
         </is>
       </c>
       <c r="B50" t="n">
-        <v>-117.0621</v>
-      </c>
-      <c r="C50" t="n">
-        <v>-446.2089</v>
-      </c>
-      <c r="D50" t="n">
-        <v>212.0848</v>
-      </c>
-      <c r="E50" t="inlineStr">
+        <v>-117.062</v>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>-446.209-212.085</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
         <is>
           <t>0.485</t>
         </is>
@@ -2856,15 +2780,14 @@
         </is>
       </c>
       <c r="B51" t="n">
-        <v>126.6878</v>
-      </c>
-      <c r="C51" t="n">
-        <v>-672.6121000000001</v>
-      </c>
-      <c r="D51" t="n">
-        <v>925.9876</v>
-      </c>
-      <c r="E51" t="inlineStr">
+        <v>126.688</v>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>-672.612-925.988</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
         <is>
           <t>0.756</t>
         </is>
@@ -2879,13 +2802,12 @@
       <c r="B52" t="n">
         <v>14.306</v>
       </c>
-      <c r="C52" t="n">
-        <v>3.5073</v>
-      </c>
-      <c r="D52" t="n">
-        <v>25.1046</v>
-      </c>
-      <c r="E52" t="inlineStr">
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>3.507-25.105</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
         <is>
           <t>0.010</t>
         </is>
@@ -2898,15 +2820,14 @@
         </is>
       </c>
       <c r="B53" t="n">
-        <v>-0.7754</v>
-      </c>
-      <c r="C53" t="n">
-        <v>-3.5976</v>
-      </c>
-      <c r="D53" t="n">
-        <v>2.0467</v>
-      </c>
-      <c r="E53" t="inlineStr">
+        <v>-0.775</v>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>-3.598-2.047</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
         <is>
           <t>0.589</t>
         </is>
@@ -2917,7 +2838,6 @@
       <c r="B54" t="inlineStr"/>
       <c r="C54" t="inlineStr"/>
       <c r="D54" t="inlineStr"/>
-      <c r="E54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55">
@@ -2927,7 +2847,6 @@
       <c r="B55" t="inlineStr"/>
       <c r="C55" t="inlineStr"/>
       <c r="D55" t="inlineStr"/>
-      <c r="E55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
@@ -2942,7 +2861,6 @@
       </c>
       <c r="C56" t="inlineStr"/>
       <c r="D56" t="inlineStr"/>
-      <c r="E56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
@@ -2957,7 +2875,6 @@
       </c>
       <c r="C57" t="inlineStr"/>
       <c r="D57" t="inlineStr"/>
-      <c r="E57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
@@ -2972,7 +2889,6 @@
       </c>
       <c r="C58" t="inlineStr"/>
       <c r="D58" t="inlineStr"/>
-      <c r="E58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
@@ -2987,7 +2903,6 @@
       </c>
       <c r="C59" t="inlineStr"/>
       <c r="D59" t="inlineStr"/>
-      <c r="E59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
@@ -2998,7 +2913,6 @@
       <c r="B60" t="inlineStr"/>
       <c r="C60" t="inlineStr"/>
       <c r="D60" t="inlineStr"/>
-      <c r="E60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
@@ -3007,15 +2921,14 @@
         </is>
       </c>
       <c r="B61" t="n">
-        <v>1172.8164</v>
-      </c>
-      <c r="C61" t="n">
-        <v>334.6021</v>
-      </c>
-      <c r="D61" t="n">
-        <v>2011.0308</v>
-      </c>
-      <c r="E61" t="inlineStr">
+        <v>1172.816</v>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>334.602-2011.031</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
         <is>
           <t>0.006</t>
         </is>
@@ -3028,15 +2941,14 @@
         </is>
       </c>
       <c r="B62" t="n">
-        <v>110.4368</v>
-      </c>
-      <c r="C62" t="n">
-        <v>-111.9879</v>
-      </c>
-      <c r="D62" t="n">
-        <v>332.8615</v>
-      </c>
-      <c r="E62" t="inlineStr">
+        <v>110.437</v>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>-111.988-332.861</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
         <is>
           <t>0.329</t>
         </is>
@@ -3049,15 +2961,14 @@
         </is>
       </c>
       <c r="B63" t="n">
-        <v>539.2194</v>
-      </c>
-      <c r="C63" t="n">
-        <v>-199.436</v>
-      </c>
-      <c r="D63" t="n">
-        <v>1277.8747</v>
-      </c>
-      <c r="E63" t="inlineStr">
+        <v>539.2190000000001</v>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>-199.436-1277.875</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
         <is>
           <t>0.152</t>
         </is>
@@ -3072,13 +2983,12 @@
       <c r="B64" t="n">
         <v>13.203</v>
       </c>
-      <c r="C64" t="n">
-        <v>1.2918</v>
-      </c>
-      <c r="D64" t="n">
-        <v>25.1142</v>
-      </c>
-      <c r="E64" t="inlineStr">
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>1.292-25.114</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
         <is>
           <t>0.030</t>
         </is>
@@ -3091,15 +3001,14 @@
         </is>
       </c>
       <c r="B65" t="n">
-        <v>-0.9345</v>
-      </c>
-      <c r="C65" t="n">
-        <v>-4.0656</v>
-      </c>
-      <c r="D65" t="n">
-        <v>2.1966</v>
-      </c>
-      <c r="E65" t="inlineStr">
+        <v>-0.9340000000000001</v>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>-4.066-2.197</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
         <is>
           <t>0.558</t>
         </is>
@@ -3110,7 +3019,6 @@
       <c r="B66" t="inlineStr"/>
       <c r="C66" t="inlineStr"/>
       <c r="D66" t="inlineStr"/>
-      <c r="E66" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
